--- a/customer.xlsx
+++ b/customer.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{634BBD11-193B-4113-92BA-D9F30B575692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="163">
   <si>
     <t>고객사명:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -663,13 +669,21 @@
   </si>
   <si>
     <t>사내규격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트용 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1028,15 +1042,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -2184,6 +2198,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/customer.xlsx
+++ b/customer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{634BBD11-193B-4113-92BA-D9F30B575692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9D1B7-E8C8-4022-A08D-BAB232115923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="176">
   <si>
     <t>고객사명:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -678,6 +678,53 @@
   <si>
     <t>테스트1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트10</t>
+  </si>
+  <si>
+    <t>테스트11</t>
+  </si>
+  <si>
+    <t>테스트12</t>
+  </si>
+  <si>
+    <t>테스트13</t>
+  </si>
+  <si>
+    <t>테스트14</t>
   </si>
 </sst>
 </file>
@@ -2205,6 +2252,45 @@
       <c r="B25" t="s">
         <v>162</v>
       </c>
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" t="s">
+        <v>170</v>
+      </c>
+      <c r="K25" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" t="s">
+        <v>172</v>
+      </c>
+      <c r="M25" t="s">
+        <v>173</v>
+      </c>
+      <c r="N25" t="s">
+        <v>174</v>
+      </c>
+      <c r="O25" t="s">
+        <v>175</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/customer.xlsx
+++ b/customer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9D1B7-E8C8-4022-A08D-BAB232115923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1071AB-54A2-4C65-8AF5-31DDE99375DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="164">
   <si>
     <t>고객사명:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -672,59 +672,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>테스트용 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트10</t>
-  </si>
-  <si>
-    <t>테스트11</t>
-  </si>
-  <si>
-    <t>테스트12</t>
-  </si>
-  <si>
-    <t>테스트13</t>
-  </si>
-  <si>
-    <t>테스트14</t>
+    <t>일반품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴㅇ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅏ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2256,41 +2213,21 @@
         <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H25" t="s">
-        <v>168</v>
-      </c>
-      <c r="I25" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" t="s">
-        <v>170</v>
-      </c>
-      <c r="K25" t="s">
-        <v>171</v>
-      </c>
-      <c r="L25" t="s">
-        <v>172</v>
-      </c>
-      <c r="M25" t="s">
-        <v>173</v>
-      </c>
-      <c r="N25" t="s">
-        <v>174</v>
-      </c>
-      <c r="O25" t="s">
-        <v>175</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O25" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
